--- a/results/walkforward/walk_forward_SPY.xlsx
+++ b/results/walkforward/walk_forward_SPY.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="54" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="238" uniqueCount="48">
   <si>
     <t>Ticker</t>
   </si>
@@ -70,6 +70,93 @@
   </si>
   <si>
     <t>SharpeImprovement</t>
+  </si>
+  <si>
+    <t>BaselineReturnPct</t>
+  </si>
+  <si>
+    <t>ExposureReturnPct</t>
+  </si>
+  <si>
+    <t>BaselineMaxDrawdownPct</t>
+  </si>
+  <si>
+    <t>ExposureMaxDrawdownPct</t>
+  </si>
+  <si>
+    <t>BaselineSharpe</t>
+  </si>
+  <si>
+    <t>ExposureSharpe</t>
+  </si>
+  <si>
+    <t>BuyHoldBuyCount</t>
+  </si>
+  <si>
+    <t>BaselineBuyCount</t>
+  </si>
+  <si>
+    <t>ExposureBuyCount</t>
+  </si>
+  <si>
+    <t>BuyHoldSellCount</t>
+  </si>
+  <si>
+    <t>BaselineSellCount</t>
+  </si>
+  <si>
+    <t>ExposureSellCount</t>
+  </si>
+  <si>
+    <t>BuyHoldTradeCount</t>
+  </si>
+  <si>
+    <t>BaselineTradeCount</t>
+  </si>
+  <si>
+    <t>ExposureTradeCount</t>
+  </si>
+  <si>
+    <t>BuyHoldTimeInMarketPct</t>
+  </si>
+  <si>
+    <t>BaselineTimeInMarketPct</t>
+  </si>
+  <si>
+    <t>ExposureTimeInMarketPct</t>
+  </si>
+  <si>
+    <t>ExposureAveragePct</t>
+  </si>
+  <si>
+    <t>ExposureTurnoverTotal</t>
+  </si>
+  <si>
+    <t>BuyHoldExcessReturnPct</t>
+  </si>
+  <si>
+    <t>BaselineExcessReturnPct</t>
+  </si>
+  <si>
+    <t>ExposureExcessReturnPct</t>
+  </si>
+  <si>
+    <t>BuyHoldDrawdownImprovementPct</t>
+  </si>
+  <si>
+    <t>BaselineDrawdownImprovementPct</t>
+  </si>
+  <si>
+    <t>ExposureDrawdownImprovementPct</t>
+  </si>
+  <si>
+    <t>BuyHoldSharpeImprovement</t>
+  </si>
+  <si>
+    <t>BaselineSharpeImprovement</t>
+  </si>
+  <si>
+    <t>ExposureSharpeImprovement</t>
   </si>
 </sst>
 </file>
@@ -115,7 +202,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R10"/>
+  <dimension ref="A1:AK10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5.83984375" customWidth="true"/>
@@ -123,19 +210,38 @@
     <col min="3" max="3" width="15.5234375" customWidth="true"/>
     <col min="4" max="4" width="15.5234375" customWidth="true"/>
     <col min="5" max="5" width="15.5234375" customWidth="true"/>
-    <col min="6" max="6" width="15.41796875" customWidth="true"/>
-    <col min="7" max="7" width="15.5234375" customWidth="true"/>
-    <col min="8" max="8" width="22.20703125" customWidth="true"/>
+    <col min="6" max="6" width="15.5234375" customWidth="true"/>
+    <col min="7" max="7" width="15.3671875" customWidth="true"/>
+    <col min="8" max="8" width="16.1015625" customWidth="true"/>
     <col min="9" max="9" width="22.3125" customWidth="true"/>
-    <col min="10" max="10" width="13.15625" customWidth="true"/>
-    <col min="11" max="11" width="13.20703125" customWidth="true"/>
-    <col min="12" max="12" width="8.7890625" customWidth="true"/>
-    <col min="13" max="13" width="8.5234375" customWidth="true"/>
-    <col min="14" max="14" width="10.3671875" customWidth="true"/>
-    <col min="15" max="15" width="14.734375" customWidth="true"/>
-    <col min="16" max="16" width="13.9453125" customWidth="true"/>
-    <col min="17" max="17" width="22.99609375" customWidth="true"/>
-    <col min="18" max="18" width="17.3671875" customWidth="true"/>
+    <col min="10" max="10" width="22.15625" customWidth="true"/>
+    <col min="11" max="11" width="22.89453125" customWidth="true"/>
+    <col min="12" max="12" width="13.20703125" customWidth="true"/>
+    <col min="13" max="13" width="13.15625" customWidth="true"/>
+    <col min="14" max="14" width="13.7890625" customWidth="true"/>
+    <col min="15" max="15" width="15.41796875" customWidth="true"/>
+    <col min="16" max="16" width="15.26171875" customWidth="true"/>
+    <col min="17" max="17" width="16" customWidth="true"/>
+    <col min="18" max="18" width="15.15625" customWidth="true"/>
+    <col min="19" max="19" width="15" customWidth="true"/>
+    <col min="20" max="20" width="15.734375" customWidth="true"/>
+    <col min="21" max="21" width="16.99609375" customWidth="true"/>
+    <col min="22" max="22" width="16.83984375" customWidth="true"/>
+    <col min="23" max="23" width="17.578125" customWidth="true"/>
+    <col min="24" max="24" width="21.3671875" customWidth="true"/>
+    <col min="25" max="25" width="21.20703125" customWidth="true"/>
+    <col min="26" max="26" width="21.9453125" customWidth="true"/>
+    <col min="27" max="27" width="17.20703125" customWidth="true"/>
+    <col min="28" max="28" width="19.5234375" customWidth="true"/>
+    <col min="29" max="29" width="20.578125" customWidth="true"/>
+    <col min="30" max="30" width="20.41796875" customWidth="true"/>
+    <col min="31" max="31" width="21.15625" customWidth="true"/>
+    <col min="32" max="32" width="29.62890625" customWidth="true"/>
+    <col min="33" max="33" width="29.47265625" customWidth="true"/>
+    <col min="34" max="34" width="30.20703125" customWidth="true"/>
+    <col min="35" max="35" width="23.99609375" customWidth="true"/>
+    <col min="36" max="36" width="23.83984375" customWidth="true"/>
+    <col min="37" max="37" width="24.578125" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -155,43 +261,100 @@
         <v>5</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G1" s="0" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="H1" s="0" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="I1" s="0" t="s">
         <v>9</v>
       </c>
       <c r="J1" s="0" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="K1" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="L1" s="0" t="s">
         <v>11</v>
       </c>
-      <c r="L1" s="0" t="s">
-        <v>12</v>
-      </c>
       <c r="M1" s="0" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="N1" s="0" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="O1" s="0" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="P1" s="0" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="Q1" s="0" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="R1" s="0" t="s">
-        <v>18</v>
+        <v>28</v>
+      </c>
+      <c r="S1" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="T1" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="U1" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="V1" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="W1" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="X1" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="Y1" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z1" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA1" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="AB1" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="AC1" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="AD1" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="AE1" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="AF1" s="0" t="s">
+        <v>42</v>
+      </c>
+      <c r="AG1" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="AH1" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="AI1" s="0" t="s">
+        <v>45</v>
+      </c>
+      <c r="AJ1" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="AK1" s="0" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="2">
@@ -211,43 +374,100 @@
         <v>43465</v>
       </c>
       <c r="F2" s="0">
+        <v>-4.5690856356264682</v>
+      </c>
+      <c r="G2" s="0">
         <v>-5.3677709816334573</v>
       </c>
-      <c r="G2" s="0">
-        <v>-4.5690856356264682</v>
-      </c>
       <c r="H2" s="0">
-        <v>-19.351436257194486</v>
+        <v>-4.68400989139377</v>
       </c>
       <c r="I2" s="0">
         <v>-19.351436257194486</v>
       </c>
       <c r="J2" s="0">
+        <v>-19.351436257194486</v>
+      </c>
+      <c r="K2" s="0">
+        <v>-13.90277431483451</v>
+      </c>
+      <c r="L2" s="0">
+        <v>-0.19029490039202343</v>
+      </c>
+      <c r="M2" s="0">
         <v>-0.24047415976865014</v>
       </c>
-      <c r="K2" s="0">
-        <v>-0.19029490039202343</v>
-      </c>
-      <c r="L2" s="0">
-        <v>0</v>
-      </c>
-      <c r="M2" s="0">
-        <v>1</v>
-      </c>
       <c r="N2" s="0">
-        <v>1</v>
+        <v>-0.36322213474756287</v>
       </c>
       <c r="O2" s="0">
+        <v>1</v>
+      </c>
+      <c r="P2" s="0">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="0">
+        <v>0</v>
+      </c>
+      <c r="R2" s="0">
+        <v>0</v>
+      </c>
+      <c r="S2" s="0">
+        <v>1</v>
+      </c>
+      <c r="T2" s="0">
+        <v>1</v>
+      </c>
+      <c r="U2" s="0">
+        <v>0</v>
+      </c>
+      <c r="V2" s="0">
+        <v>1</v>
+      </c>
+      <c r="W2" s="0">
+        <v>37</v>
+      </c>
+      <c r="X2" s="0">
+        <v>100</v>
+      </c>
+      <c r="Y2" s="0">
         <v>98.804780876494021</v>
       </c>
-      <c r="P2" s="0">
-        <v>-0.79868534600698915</v>
-      </c>
-      <c r="Q2" s="0">
-        <v>0</v>
-      </c>
-      <c r="R2" s="0">
+      <c r="Z2" s="0">
+        <v>98.804780876494021</v>
+      </c>
+      <c r="AA2" s="0">
+        <v>73.944223107569712</v>
+      </c>
+      <c r="AB2" s="0">
+        <v>6.9499999999999993</v>
+      </c>
+      <c r="AC2" s="0">
+        <v>0</v>
+      </c>
+      <c r="AD2" s="0">
+        <v>-0.79868534600698871</v>
+      </c>
+      <c r="AE2" s="0">
+        <v>-0.11492425576730136</v>
+      </c>
+      <c r="AF2" s="0">
+        <v>0</v>
+      </c>
+      <c r="AG2" s="0">
+        <v>0</v>
+      </c>
+      <c r="AH2" s="0">
+        <v>5.448661942359978</v>
+      </c>
+      <c r="AI2" s="0">
+        <v>0</v>
+      </c>
+      <c r="AJ2" s="0">
         <v>-0.050179259376626706</v>
+      </c>
+      <c r="AK2" s="0">
+        <v>-0.17292723435553944</v>
       </c>
     </row>
     <row r="3">
@@ -267,43 +487,100 @@
         <v>43830</v>
       </c>
       <c r="F3" s="0">
+        <v>31.221575745812657</v>
+      </c>
+      <c r="G3" s="0">
         <v>27.598956642708174</v>
       </c>
-      <c r="G3" s="0">
-        <v>31.221575745812657</v>
-      </c>
       <c r="H3" s="0">
-        <v>-6.6194338784514422</v>
+        <v>20.729538608660604</v>
       </c>
       <c r="I3" s="0">
         <v>-6.6194338784514422</v>
       </c>
       <c r="J3" s="0">
+        <v>-6.6194338784514422</v>
+      </c>
+      <c r="K3" s="0">
+        <v>-5.0327411836045943</v>
+      </c>
+      <c r="L3" s="0">
+        <v>2.235235634639432</v>
+      </c>
+      <c r="M3" s="0">
         <v>2.1299387976520467</v>
       </c>
-      <c r="K3" s="0">
-        <v>2.235235634639432</v>
-      </c>
-      <c r="L3" s="0">
-        <v>1</v>
-      </c>
-      <c r="M3" s="0">
-        <v>0</v>
-      </c>
       <c r="N3" s="0">
-        <v>1</v>
+        <v>2.2097005104154857</v>
       </c>
       <c r="O3" s="0">
+        <v>1</v>
+      </c>
+      <c r="P3" s="0">
+        <v>1</v>
+      </c>
+      <c r="Q3" s="0">
+        <v>1</v>
+      </c>
+      <c r="R3" s="0">
+        <v>0</v>
+      </c>
+      <c r="S3" s="0">
+        <v>0</v>
+      </c>
+      <c r="T3" s="0">
+        <v>0</v>
+      </c>
+      <c r="U3" s="0">
+        <v>0</v>
+      </c>
+      <c r="V3" s="0">
+        <v>1</v>
+      </c>
+      <c r="W3" s="0">
+        <v>28</v>
+      </c>
+      <c r="X3" s="0">
+        <v>100</v>
+      </c>
+      <c r="Y3" s="0">
         <v>98.412698412698404</v>
       </c>
-      <c r="P3" s="0">
-        <v>-3.6226191031044834</v>
-      </c>
-      <c r="Q3" s="0">
-        <v>0</v>
-      </c>
-      <c r="R3" s="0">
+      <c r="Z3" s="0">
+        <v>98.412698412698404</v>
+      </c>
+      <c r="AA3" s="0">
+        <v>78.234126984126988</v>
+      </c>
+      <c r="AB3" s="0">
+        <v>6.1499999999999995</v>
+      </c>
+      <c r="AC3" s="0">
+        <v>0</v>
+      </c>
+      <c r="AD3" s="0">
+        <v>-3.6226191031044852</v>
+      </c>
+      <c r="AE3" s="0">
+        <v>-10.492037137152055</v>
+      </c>
+      <c r="AF3" s="0">
+        <v>0</v>
+      </c>
+      <c r="AG3" s="0">
+        <v>0</v>
+      </c>
+      <c r="AH3" s="0">
+        <v>1.5866926948468474</v>
+      </c>
+      <c r="AI3" s="0">
+        <v>0</v>
+      </c>
+      <c r="AJ3" s="0">
         <v>-0.10529683698738523</v>
+      </c>
+      <c r="AK3" s="0">
+        <v>-0.025535124223946326</v>
       </c>
     </row>
     <row r="4">
@@ -323,43 +600,100 @@
         <v>44196</v>
       </c>
       <c r="F4" s="0">
+        <v>18.335809706936089</v>
+      </c>
+      <c r="G4" s="0">
         <v>44.259680131501035</v>
       </c>
-      <c r="G4" s="0">
-        <v>18.335809706936089</v>
-      </c>
       <c r="H4" s="0">
-        <v>-12.430243974198675</v>
+        <v>32.41378609127716</v>
       </c>
       <c r="I4" s="0">
         <v>-33.715385820778579</v>
       </c>
       <c r="J4" s="0">
+        <v>-12.430243974198675</v>
+      </c>
+      <c r="K4" s="0">
+        <v>-8.3994792939724121</v>
+      </c>
+      <c r="L4" s="0">
+        <v>0.67018718454210757</v>
+      </c>
+      <c r="M4" s="0">
         <v>1.7876808309470249</v>
       </c>
-      <c r="K4" s="0">
-        <v>0.67018718454210757</v>
-      </c>
-      <c r="L4" s="0">
-        <v>1</v>
-      </c>
-      <c r="M4" s="0">
-        <v>1</v>
-      </c>
       <c r="N4" s="0">
+        <v>1.6802033925990403</v>
+      </c>
+      <c r="O4" s="0">
+        <v>1</v>
+      </c>
+      <c r="P4" s="0">
+        <v>1</v>
+      </c>
+      <c r="Q4" s="0">
+        <v>1</v>
+      </c>
+      <c r="R4" s="0">
+        <v>0</v>
+      </c>
+      <c r="S4" s="0">
+        <v>1</v>
+      </c>
+      <c r="T4" s="0">
+        <v>1</v>
+      </c>
+      <c r="U4" s="0">
+        <v>0</v>
+      </c>
+      <c r="V4" s="0">
         <v>2</v>
       </c>
-      <c r="O4" s="0">
+      <c r="W4" s="0">
+        <v>37</v>
+      </c>
+      <c r="X4" s="0">
+        <v>100</v>
+      </c>
+      <c r="Y4" s="0">
         <v>92.490118577075094</v>
       </c>
-      <c r="P4" s="0">
-        <v>25.923870424564946</v>
-      </c>
-      <c r="Q4" s="0">
+      <c r="Z4" s="0">
+        <v>92.490118577075094</v>
+      </c>
+      <c r="AA4" s="0">
+        <v>73.577075098814234</v>
+      </c>
+      <c r="AB4" s="0">
+        <v>7.8999999999999995</v>
+      </c>
+      <c r="AC4" s="0">
+        <v>0</v>
+      </c>
+      <c r="AD4" s="0">
+        <v>25.923870424564942</v>
+      </c>
+      <c r="AE4" s="0">
+        <v>14.077976384341074</v>
+      </c>
+      <c r="AF4" s="0">
+        <v>0</v>
+      </c>
+      <c r="AG4" s="0">
         <v>21.285141846579904</v>
       </c>
-      <c r="R4" s="0">
+      <c r="AH4" s="0">
+        <v>25.315906526806163</v>
+      </c>
+      <c r="AI4" s="0">
+        <v>0</v>
+      </c>
+      <c r="AJ4" s="0">
         <v>1.1174936464049172</v>
+      </c>
+      <c r="AK4" s="0">
+        <v>1.0100162080569328</v>
       </c>
     </row>
     <row r="5">
@@ -385,28 +719,28 @@
         <v>28.732781664834683</v>
       </c>
       <c r="H5" s="0">
-        <v>-5.1143070679695146</v>
+        <v>19.021325523263897</v>
       </c>
       <c r="I5" s="0">
         <v>-5.1143070679695146</v>
       </c>
       <c r="J5" s="0">
+        <v>-5.1143070679695146</v>
+      </c>
+      <c r="K5" s="0">
+        <v>-3.6882054660242525</v>
+      </c>
+      <c r="L5" s="0">
         <v>2.0107261521397488</v>
       </c>
-      <c r="K5" s="0">
+      <c r="M5" s="0">
         <v>2.0107261521397488</v>
       </c>
-      <c r="L5" s="0">
-        <v>0</v>
-      </c>
-      <c r="M5" s="0">
-        <v>0</v>
-      </c>
       <c r="N5" s="0">
-        <v>0</v>
+        <v>1.8731720969952641</v>
       </c>
       <c r="O5" s="0">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="P5" s="0">
         <v>0</v>
@@ -416,6 +750,63 @@
       </c>
       <c r="R5" s="0">
         <v>0</v>
+      </c>
+      <c r="S5" s="0">
+        <v>0</v>
+      </c>
+      <c r="T5" s="0">
+        <v>0</v>
+      </c>
+      <c r="U5" s="0">
+        <v>0</v>
+      </c>
+      <c r="V5" s="0">
+        <v>0</v>
+      </c>
+      <c r="W5" s="0">
+        <v>28</v>
+      </c>
+      <c r="X5" s="0">
+        <v>100</v>
+      </c>
+      <c r="Y5" s="0">
+        <v>100</v>
+      </c>
+      <c r="Z5" s="0">
+        <v>100</v>
+      </c>
+      <c r="AA5" s="0">
+        <v>78.015873015873026</v>
+      </c>
+      <c r="AB5" s="0">
+        <v>5.3999999999999986</v>
+      </c>
+      <c r="AC5" s="0">
+        <v>0</v>
+      </c>
+      <c r="AD5" s="0">
+        <v>0</v>
+      </c>
+      <c r="AE5" s="0">
+        <v>-9.7114561415707854</v>
+      </c>
+      <c r="AF5" s="0">
+        <v>0</v>
+      </c>
+      <c r="AG5" s="0">
+        <v>0</v>
+      </c>
+      <c r="AH5" s="0">
+        <v>1.4261016019452621</v>
+      </c>
+      <c r="AI5" s="0">
+        <v>0</v>
+      </c>
+      <c r="AJ5" s="0">
+        <v>0</v>
+      </c>
+      <c r="AK5" s="0">
+        <v>-0.13755405514448471</v>
       </c>
     </row>
     <row r="6">
@@ -435,43 +826,100 @@
         <v>44926</v>
       </c>
       <c r="F6" s="0">
+        <v>-18.172028536815223</v>
+      </c>
+      <c r="G6" s="0">
         <v>-15.637795904287955</v>
       </c>
-      <c r="G6" s="0">
-        <v>-18.172028536815223</v>
-      </c>
       <c r="H6" s="0">
-        <v>-24.07360476659418</v>
+        <v>-12.677420873449552</v>
       </c>
       <c r="I6" s="0">
         <v>-24.495450885579995</v>
       </c>
       <c r="J6" s="0">
+        <v>-24.07360476659418</v>
+      </c>
+      <c r="K6" s="0">
+        <v>-18.049438969990838</v>
+      </c>
+      <c r="L6" s="0">
+        <v>-0.70940817269533907</v>
+      </c>
+      <c r="M6" s="0">
         <v>-0.68843779145003703</v>
       </c>
-      <c r="K6" s="0">
-        <v>-0.70940817269533907</v>
-      </c>
-      <c r="L6" s="0">
+      <c r="N6" s="0">
+        <v>-0.79842668101216141</v>
+      </c>
+      <c r="O6" s="0">
+        <v>1</v>
+      </c>
+      <c r="P6" s="0">
         <v>3</v>
       </c>
-      <c r="M6" s="0">
+      <c r="Q6" s="0">
         <v>3</v>
       </c>
-      <c r="N6" s="0">
+      <c r="R6" s="0">
+        <v>0</v>
+      </c>
+      <c r="S6" s="0">
+        <v>3</v>
+      </c>
+      <c r="T6" s="0">
+        <v>3</v>
+      </c>
+      <c r="U6" s="0">
+        <v>0</v>
+      </c>
+      <c r="V6" s="0">
         <v>6</v>
       </c>
-      <c r="O6" s="0">
+      <c r="W6" s="0">
+        <v>49</v>
+      </c>
+      <c r="X6" s="0">
+        <v>100</v>
+      </c>
+      <c r="Y6" s="0">
         <v>82.470119521912352</v>
       </c>
-      <c r="P6" s="0">
-        <v>2.5342326325272673</v>
-      </c>
-      <c r="Q6" s="0">
-        <v>0.42184611898581537</v>
-      </c>
-      <c r="R6" s="0">
+      <c r="Z6" s="0">
+        <v>82.470119521912352</v>
+      </c>
+      <c r="AA6" s="0">
+        <v>60.657370517928314</v>
+      </c>
+      <c r="AB6" s="0">
+        <v>11.299999999999999</v>
+      </c>
+      <c r="AC6" s="0">
+        <v>0</v>
+      </c>
+      <c r="AD6" s="0">
+        <v>2.5342326325272668</v>
+      </c>
+      <c r="AE6" s="0">
+        <v>5.4946076633656693</v>
+      </c>
+      <c r="AF6" s="0">
+        <v>0</v>
+      </c>
+      <c r="AG6" s="0">
+        <v>0.42184611898581359</v>
+      </c>
+      <c r="AH6" s="0">
+        <v>6.446011915589156</v>
+      </c>
+      <c r="AI6" s="0">
+        <v>0</v>
+      </c>
+      <c r="AJ6" s="0">
         <v>0.020970381245302039</v>
+      </c>
+      <c r="AK6" s="0">
+        <v>-0.089018508316822342</v>
       </c>
     </row>
     <row r="7">
@@ -497,28 +945,28 @@
         <v>26.175843201130313</v>
       </c>
       <c r="H7" s="0">
-        <v>-9.9744880277077392</v>
+        <v>20.335896636640239</v>
       </c>
       <c r="I7" s="0">
         <v>-9.9744880277077392</v>
       </c>
       <c r="J7" s="0">
+        <v>-9.9744880277077392</v>
+      </c>
+      <c r="K7" s="0">
+        <v>-7.6281589788756321</v>
+      </c>
+      <c r="L7" s="0">
         <v>1.8582694680421219</v>
       </c>
-      <c r="K7" s="0">
+      <c r="M7" s="0">
         <v>1.8582694680421219</v>
       </c>
-      <c r="L7" s="0">
-        <v>0</v>
-      </c>
-      <c r="M7" s="0">
-        <v>0</v>
-      </c>
       <c r="N7" s="0">
-        <v>0</v>
+        <v>1.879718964501303</v>
       </c>
       <c r="O7" s="0">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="P7" s="0">
         <v>0</v>
@@ -528,6 +976,63 @@
       </c>
       <c r="R7" s="0">
         <v>0</v>
+      </c>
+      <c r="S7" s="0">
+        <v>0</v>
+      </c>
+      <c r="T7" s="0">
+        <v>0</v>
+      </c>
+      <c r="U7" s="0">
+        <v>0</v>
+      </c>
+      <c r="V7" s="0">
+        <v>0</v>
+      </c>
+      <c r="W7" s="0">
+        <v>31</v>
+      </c>
+      <c r="X7" s="0">
+        <v>100</v>
+      </c>
+      <c r="Y7" s="0">
+        <v>100</v>
+      </c>
+      <c r="Z7" s="0">
+        <v>100</v>
+      </c>
+      <c r="AA7" s="0">
+        <v>78.02000000000001</v>
+      </c>
+      <c r="AB7" s="0">
+        <v>5.5999999999999996</v>
+      </c>
+      <c r="AC7" s="0">
+        <v>0</v>
+      </c>
+      <c r="AD7" s="0">
+        <v>0</v>
+      </c>
+      <c r="AE7" s="0">
+        <v>-5.8399465644900728</v>
+      </c>
+      <c r="AF7" s="0">
+        <v>0</v>
+      </c>
+      <c r="AG7" s="0">
+        <v>0</v>
+      </c>
+      <c r="AH7" s="0">
+        <v>2.3463290488321076</v>
+      </c>
+      <c r="AI7" s="0">
+        <v>0</v>
+      </c>
+      <c r="AJ7" s="0">
+        <v>0</v>
+      </c>
+      <c r="AK7" s="0">
+        <v>0.02144949645918115</v>
       </c>
     </row>
     <row r="8">
@@ -553,28 +1058,28 @@
         <v>24.886296603431646</v>
       </c>
       <c r="H8" s="0">
-        <v>-8.4055178970657511</v>
+        <v>17.560142406627179</v>
       </c>
       <c r="I8" s="0">
         <v>-8.4055178970657511</v>
       </c>
       <c r="J8" s="0">
+        <v>-8.4055178970657511</v>
+      </c>
+      <c r="K8" s="0">
+        <v>-6.0885923685488503</v>
+      </c>
+      <c r="L8" s="0">
         <v>1.8316019878865235</v>
       </c>
-      <c r="K8" s="0">
+      <c r="M8" s="0">
         <v>1.8316019878865235</v>
       </c>
-      <c r="L8" s="0">
-        <v>0</v>
-      </c>
-      <c r="M8" s="0">
-        <v>0</v>
-      </c>
       <c r="N8" s="0">
-        <v>0</v>
+        <v>1.8012791521412292</v>
       </c>
       <c r="O8" s="0">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="P8" s="0">
         <v>0</v>
@@ -584,6 +1089,63 @@
       </c>
       <c r="R8" s="0">
         <v>0</v>
+      </c>
+      <c r="S8" s="0">
+        <v>0</v>
+      </c>
+      <c r="T8" s="0">
+        <v>0</v>
+      </c>
+      <c r="U8" s="0">
+        <v>0</v>
+      </c>
+      <c r="V8" s="0">
+        <v>0</v>
+      </c>
+      <c r="W8" s="0">
+        <v>33</v>
+      </c>
+      <c r="X8" s="0">
+        <v>100</v>
+      </c>
+      <c r="Y8" s="0">
+        <v>100</v>
+      </c>
+      <c r="Z8" s="0">
+        <v>100</v>
+      </c>
+      <c r="AA8" s="0">
+        <v>77.817460317460345</v>
+      </c>
+      <c r="AB8" s="0">
+        <v>6.0999999999999988</v>
+      </c>
+      <c r="AC8" s="0">
+        <v>0</v>
+      </c>
+      <c r="AD8" s="0">
+        <v>0</v>
+      </c>
+      <c r="AE8" s="0">
+        <v>-7.3261541968044686</v>
+      </c>
+      <c r="AF8" s="0">
+        <v>0</v>
+      </c>
+      <c r="AG8" s="0">
+        <v>0</v>
+      </c>
+      <c r="AH8" s="0">
+        <v>2.3169255285168999</v>
+      </c>
+      <c r="AI8" s="0">
+        <v>0</v>
+      </c>
+      <c r="AJ8" s="0">
+        <v>0</v>
+      </c>
+      <c r="AK8" s="0">
+        <v>-0.030322835745294263</v>
       </c>
     </row>
     <row r="9">
@@ -609,28 +1171,28 @@
         <v>16.702577170503385</v>
       </c>
       <c r="H9" s="0">
-        <v>-18.755277437767138</v>
+        <v>8.4690283957127086</v>
       </c>
       <c r="I9" s="0">
         <v>-18.755277437767138</v>
       </c>
       <c r="J9" s="0">
+        <v>-18.755277437767138</v>
+      </c>
+      <c r="K9" s="0">
+        <v>-14.200548002191216</v>
+      </c>
+      <c r="L9" s="0">
         <v>0.89546472171375724</v>
       </c>
-      <c r="K9" s="0">
+      <c r="M9" s="0">
         <v>0.89546472171375724</v>
       </c>
-      <c r="L9" s="0">
-        <v>0</v>
-      </c>
-      <c r="M9" s="0">
-        <v>0</v>
-      </c>
       <c r="N9" s="0">
-        <v>0</v>
+        <v>0.68956474035617243</v>
       </c>
       <c r="O9" s="0">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="P9" s="0">
         <v>0</v>
@@ -640,6 +1202,63 @@
       </c>
       <c r="R9" s="0">
         <v>0</v>
+      </c>
+      <c r="S9" s="0">
+        <v>0</v>
+      </c>
+      <c r="T9" s="0">
+        <v>0</v>
+      </c>
+      <c r="U9" s="0">
+        <v>0</v>
+      </c>
+      <c r="V9" s="0">
+        <v>0</v>
+      </c>
+      <c r="W9" s="0">
+        <v>41</v>
+      </c>
+      <c r="X9" s="0">
+        <v>100</v>
+      </c>
+      <c r="Y9" s="0">
+        <v>100</v>
+      </c>
+      <c r="Z9" s="0">
+        <v>100</v>
+      </c>
+      <c r="AA9" s="0">
+        <v>77.30000000000004</v>
+      </c>
+      <c r="AB9" s="0">
+        <v>7.5999999999999988</v>
+      </c>
+      <c r="AC9" s="0">
+        <v>0</v>
+      </c>
+      <c r="AD9" s="0">
+        <v>0</v>
+      </c>
+      <c r="AE9" s="0">
+        <v>-8.2335487747906768</v>
+      </c>
+      <c r="AF9" s="0">
+        <v>0</v>
+      </c>
+      <c r="AG9" s="0">
+        <v>0</v>
+      </c>
+      <c r="AH9" s="0">
+        <v>4.554729435575922</v>
+      </c>
+      <c r="AI9" s="0">
+        <v>0</v>
+      </c>
+      <c r="AJ9" s="0">
+        <v>0</v>
+      </c>
+      <c r="AK9" s="0">
+        <v>-0.2058999813575848</v>
       </c>
     </row>
     <row r="10">
@@ -665,28 +1284,28 @@
         <v>10.932367433130064</v>
       </c>
       <c r="H10" s="0">
-        <v>-9.1331291607355318</v>
+        <v>8.8050500761055019</v>
       </c>
       <c r="I10" s="0">
         <v>-9.1331291607355318</v>
       </c>
       <c r="J10" s="0">
+        <v>-9.1331291607355318</v>
+      </c>
+      <c r="K10" s="0">
+        <v>-7.4670309512922639</v>
+      </c>
+      <c r="L10" s="0">
         <v>1.968059254099956</v>
       </c>
-      <c r="K10" s="0">
+      <c r="M10" s="0">
         <v>1.968059254099956</v>
       </c>
-      <c r="L10" s="0">
-        <v>0</v>
-      </c>
-      <c r="M10" s="0">
-        <v>0</v>
-      </c>
       <c r="N10" s="0">
-        <v>0</v>
+        <v>2.0960494697801262</v>
       </c>
       <c r="O10" s="0">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="P10" s="0">
         <v>0</v>
@@ -696,6 +1315,63 @@
       </c>
       <c r="R10" s="0">
         <v>0</v>
+      </c>
+      <c r="S10" s="0">
+        <v>0</v>
+      </c>
+      <c r="T10" s="0">
+        <v>0</v>
+      </c>
+      <c r="U10" s="0">
+        <v>0</v>
+      </c>
+      <c r="V10" s="0">
+        <v>0</v>
+      </c>
+      <c r="W10" s="0">
+        <v>12</v>
+      </c>
+      <c r="X10" s="0">
+        <v>100</v>
+      </c>
+      <c r="Y10" s="0">
+        <v>100</v>
+      </c>
+      <c r="Z10" s="0">
+        <v>100</v>
+      </c>
+      <c r="AA10" s="0">
+        <v>77.79411764705884</v>
+      </c>
+      <c r="AB10" s="0">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="AC10" s="0">
+        <v>0</v>
+      </c>
+      <c r="AD10" s="0">
+        <v>0</v>
+      </c>
+      <c r="AE10" s="0">
+        <v>-2.1273173570245607</v>
+      </c>
+      <c r="AF10" s="0">
+        <v>0</v>
+      </c>
+      <c r="AG10" s="0">
+        <v>0</v>
+      </c>
+      <c r="AH10" s="0">
+        <v>1.6660982094432675</v>
+      </c>
+      <c r="AI10" s="0">
+        <v>0</v>
+      </c>
+      <c r="AJ10" s="0">
+        <v>0</v>
+      </c>
+      <c r="AK10" s="0">
+        <v>0.12799021568017022</v>
       </c>
     </row>
   </sheetData>

--- a/results/walkforward/walk_forward_SPY.xlsx
+++ b/results/walkforward/walk_forward_SPY.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="238" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="330" uniqueCount="48">
   <si>
     <t>Ticker</t>
   </si>
@@ -380,7 +380,7 @@
         <v>-5.3677709816334573</v>
       </c>
       <c r="H2" s="0">
-        <v>-4.68400989139377</v>
+        <v>-8.8923616416908597</v>
       </c>
       <c r="I2" s="0">
         <v>-19.351436257194486</v>
@@ -389,7 +389,7 @@
         <v>-19.351436257194486</v>
       </c>
       <c r="K2" s="0">
-        <v>-13.90277431483451</v>
+        <v>-18.463481532639747</v>
       </c>
       <c r="L2" s="0">
         <v>-0.19029490039202343</v>
@@ -398,7 +398,7 @@
         <v>-0.24047415976865014</v>
       </c>
       <c r="N2" s="0">
-        <v>-0.36322213474756287</v>
+        <v>-0.50205518718021203</v>
       </c>
       <c r="O2" s="0">
         <v>1</v>
@@ -425,7 +425,7 @@
         <v>1</v>
       </c>
       <c r="W2" s="0">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="X2" s="0">
         <v>100</v>
@@ -437,10 +437,10 @@
         <v>98.804780876494021</v>
       </c>
       <c r="AA2" s="0">
-        <v>73.944223107569712</v>
+        <v>97.111553784860561</v>
       </c>
       <c r="AB2" s="0">
-        <v>6.9499999999999993</v>
+        <v>3.5</v>
       </c>
       <c r="AC2" s="0">
         <v>0</v>
@@ -449,7 +449,7 @@
         <v>-0.79868534600698871</v>
       </c>
       <c r="AE2" s="0">
-        <v>-0.11492425576730136</v>
+        <v>-4.3232760060643916</v>
       </c>
       <c r="AF2" s="0">
         <v>0</v>
@@ -458,7 +458,7 @@
         <v>0</v>
       </c>
       <c r="AH2" s="0">
-        <v>5.448661942359978</v>
+        <v>0.88795472455474034</v>
       </c>
       <c r="AI2" s="0">
         <v>0</v>
@@ -467,7 +467,7 @@
         <v>-0.050179259376626706</v>
       </c>
       <c r="AK2" s="0">
-        <v>-0.17292723435553944</v>
+        <v>-0.31176028678818857</v>
       </c>
     </row>
     <row r="3">
@@ -493,7 +493,7 @@
         <v>27.598956642708174</v>
       </c>
       <c r="H3" s="0">
-        <v>20.729538608660604</v>
+        <v>27.598956642708174</v>
       </c>
       <c r="I3" s="0">
         <v>-6.6194338784514422</v>
@@ -502,7 +502,7 @@
         <v>-6.6194338784514422</v>
       </c>
       <c r="K3" s="0">
-        <v>-5.0327411836045943</v>
+        <v>-6.6194338784514422</v>
       </c>
       <c r="L3" s="0">
         <v>2.235235634639432</v>
@@ -511,7 +511,7 @@
         <v>2.1299387976520467</v>
       </c>
       <c r="N3" s="0">
-        <v>2.2097005104154857</v>
+        <v>2.1299387976520467</v>
       </c>
       <c r="O3" s="0">
         <v>1</v>
@@ -538,7 +538,7 @@
         <v>1</v>
       </c>
       <c r="W3" s="0">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="X3" s="0">
         <v>100</v>
@@ -550,10 +550,10 @@
         <v>98.412698412698404</v>
       </c>
       <c r="AA3" s="0">
-        <v>78.234126984126988</v>
+        <v>98.412698412698404</v>
       </c>
       <c r="AB3" s="0">
-        <v>6.1499999999999995</v>
+        <v>1</v>
       </c>
       <c r="AC3" s="0">
         <v>0</v>
@@ -562,7 +562,7 @@
         <v>-3.6226191031044852</v>
       </c>
       <c r="AE3" s="0">
-        <v>-10.492037137152055</v>
+        <v>-3.6226191031044852</v>
       </c>
       <c r="AF3" s="0">
         <v>0</v>
@@ -571,7 +571,7 @@
         <v>0</v>
       </c>
       <c r="AH3" s="0">
-        <v>1.5866926948468474</v>
+        <v>0</v>
       </c>
       <c r="AI3" s="0">
         <v>0</v>
@@ -580,7 +580,7 @@
         <v>-0.10529683698738523</v>
       </c>
       <c r="AK3" s="0">
-        <v>-0.025535124223946326</v>
+        <v>-0.10529683698738523</v>
       </c>
     </row>
     <row r="4">
@@ -606,7 +606,7 @@
         <v>44.259680131501035</v>
       </c>
       <c r="H4" s="0">
-        <v>32.41378609127716</v>
+        <v>41.868006425993244</v>
       </c>
       <c r="I4" s="0">
         <v>-33.715385820778579</v>
@@ -615,7 +615,7 @@
         <v>-12.430243974198675</v>
       </c>
       <c r="K4" s="0">
-        <v>-8.3994792939724121</v>
+        <v>-12.452228914892061</v>
       </c>
       <c r="L4" s="0">
         <v>0.67018718454210757</v>
@@ -624,7 +624,7 @@
         <v>1.7876808309470249</v>
       </c>
       <c r="N4" s="0">
-        <v>1.6802033925990403</v>
+        <v>1.7730547926263396</v>
       </c>
       <c r="O4" s="0">
         <v>1</v>
@@ -651,7 +651,7 @@
         <v>2</v>
       </c>
       <c r="W4" s="0">
-        <v>37</v>
+        <v>6</v>
       </c>
       <c r="X4" s="0">
         <v>100</v>
@@ -663,10 +663,10 @@
         <v>92.490118577075094</v>
       </c>
       <c r="AA4" s="0">
-        <v>73.577075098814234</v>
+        <v>91.699604743083</v>
       </c>
       <c r="AB4" s="0">
-        <v>7.8999999999999995</v>
+        <v>2.5</v>
       </c>
       <c r="AC4" s="0">
         <v>0</v>
@@ -675,7 +675,7 @@
         <v>25.923870424564942</v>
       </c>
       <c r="AE4" s="0">
-        <v>14.077976384341074</v>
+        <v>23.532196719057154</v>
       </c>
       <c r="AF4" s="0">
         <v>0</v>
@@ -684,7 +684,7 @@
         <v>21.285141846579904</v>
       </c>
       <c r="AH4" s="0">
-        <v>25.315906526806163</v>
+        <v>21.263156905886515</v>
       </c>
       <c r="AI4" s="0">
         <v>0</v>
@@ -693,7 +693,7 @@
         <v>1.1174936464049172</v>
       </c>
       <c r="AK4" s="0">
-        <v>1.0100162080569328</v>
+        <v>1.1028676080842321</v>
       </c>
     </row>
     <row r="5">
@@ -719,7 +719,7 @@
         <v>28.732781664834683</v>
       </c>
       <c r="H5" s="0">
-        <v>19.021325523263897</v>
+        <v>28.732781664834683</v>
       </c>
       <c r="I5" s="0">
         <v>-5.1143070679695146</v>
@@ -728,7 +728,7 @@
         <v>-5.1143070679695146</v>
       </c>
       <c r="K5" s="0">
-        <v>-3.6882054660242525</v>
+        <v>-5.1143070679695146</v>
       </c>
       <c r="L5" s="0">
         <v>2.0107261521397488</v>
@@ -737,7 +737,7 @@
         <v>2.0107261521397488</v>
       </c>
       <c r="N5" s="0">
-        <v>1.8731720969952641</v>
+        <v>2.0107261521397488</v>
       </c>
       <c r="O5" s="0">
         <v>1</v>
@@ -764,7 +764,7 @@
         <v>0</v>
       </c>
       <c r="W5" s="0">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="X5" s="0">
         <v>100</v>
@@ -776,10 +776,10 @@
         <v>100</v>
       </c>
       <c r="AA5" s="0">
-        <v>78.015873015873026</v>
+        <v>100</v>
       </c>
       <c r="AB5" s="0">
-        <v>5.3999999999999986</v>
+        <v>0</v>
       </c>
       <c r="AC5" s="0">
         <v>0</v>
@@ -788,7 +788,7 @@
         <v>0</v>
       </c>
       <c r="AE5" s="0">
-        <v>-9.7114561415707854</v>
+        <v>0</v>
       </c>
       <c r="AF5" s="0">
         <v>0</v>
@@ -797,7 +797,7 @@
         <v>0</v>
       </c>
       <c r="AH5" s="0">
-        <v>1.4261016019452621</v>
+        <v>0</v>
       </c>
       <c r="AI5" s="0">
         <v>0</v>
@@ -806,7 +806,7 @@
         <v>0</v>
       </c>
       <c r="AK5" s="0">
-        <v>-0.13755405514448471</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -832,7 +832,7 @@
         <v>-15.637795904287955</v>
       </c>
       <c r="H6" s="0">
-        <v>-12.677420873449552</v>
+        <v>-17.834736263905871</v>
       </c>
       <c r="I6" s="0">
         <v>-24.495450885579995</v>
@@ -841,7 +841,7 @@
         <v>-24.07360476659418</v>
       </c>
       <c r="K6" s="0">
-        <v>-18.049438969990838</v>
+        <v>-24.894281809042052</v>
       </c>
       <c r="L6" s="0">
         <v>-0.70940817269533907</v>
@@ -850,7 +850,7 @@
         <v>-0.68843779145003703</v>
       </c>
       <c r="N6" s="0">
-        <v>-0.79842668101216141</v>
+        <v>-0.8262770064734658</v>
       </c>
       <c r="O6" s="0">
         <v>1</v>
@@ -877,7 +877,7 @@
         <v>6</v>
       </c>
       <c r="W6" s="0">
-        <v>49</v>
+        <v>14</v>
       </c>
       <c r="X6" s="0">
         <v>100</v>
@@ -889,10 +889,10 @@
         <v>82.470119521912352</v>
       </c>
       <c r="AA6" s="0">
-        <v>60.657370517928314</v>
+        <v>80.478087649402383</v>
       </c>
       <c r="AB6" s="0">
-        <v>11.299999999999999</v>
+        <v>6.5</v>
       </c>
       <c r="AC6" s="0">
         <v>0</v>
@@ -901,7 +901,7 @@
         <v>2.5342326325272668</v>
       </c>
       <c r="AE6" s="0">
-        <v>5.4946076633656693</v>
+        <v>0.33729227290935082</v>
       </c>
       <c r="AF6" s="0">
         <v>0</v>
@@ -910,7 +910,7 @@
         <v>0.42184611898581359</v>
       </c>
       <c r="AH6" s="0">
-        <v>6.446011915589156</v>
+        <v>-0.39883092346205684</v>
       </c>
       <c r="AI6" s="0">
         <v>0</v>
@@ -919,7 +919,7 @@
         <v>0.020970381245302039</v>
       </c>
       <c r="AK6" s="0">
-        <v>-0.089018508316822342</v>
+        <v>-0.11686883377812674</v>
       </c>
     </row>
     <row r="7">
@@ -945,7 +945,7 @@
         <v>26.175843201130313</v>
       </c>
       <c r="H7" s="0">
-        <v>20.335896636640239</v>
+        <v>26.175843201130313</v>
       </c>
       <c r="I7" s="0">
         <v>-9.9744880277077392</v>
@@ -954,7 +954,7 @@
         <v>-9.9744880277077392</v>
       </c>
       <c r="K7" s="0">
-        <v>-7.6281589788756321</v>
+        <v>-9.9744880277077392</v>
       </c>
       <c r="L7" s="0">
         <v>1.8582694680421219</v>
@@ -963,7 +963,7 @@
         <v>1.8582694680421219</v>
       </c>
       <c r="N7" s="0">
-        <v>1.879718964501303</v>
+        <v>1.8582694680421219</v>
       </c>
       <c r="O7" s="0">
         <v>1</v>
@@ -990,7 +990,7 @@
         <v>0</v>
       </c>
       <c r="W7" s="0">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="X7" s="0">
         <v>100</v>
@@ -1002,10 +1002,10 @@
         <v>100</v>
       </c>
       <c r="AA7" s="0">
-        <v>78.02000000000001</v>
+        <v>100</v>
       </c>
       <c r="AB7" s="0">
-        <v>5.5999999999999996</v>
+        <v>0</v>
       </c>
       <c r="AC7" s="0">
         <v>0</v>
@@ -1014,7 +1014,7 @@
         <v>0</v>
       </c>
       <c r="AE7" s="0">
-        <v>-5.8399465644900728</v>
+        <v>0</v>
       </c>
       <c r="AF7" s="0">
         <v>0</v>
@@ -1023,7 +1023,7 @@
         <v>0</v>
       </c>
       <c r="AH7" s="0">
-        <v>2.3463290488321076</v>
+        <v>0</v>
       </c>
       <c r="AI7" s="0">
         <v>0</v>
@@ -1032,7 +1032,7 @@
         <v>0</v>
       </c>
       <c r="AK7" s="0">
-        <v>0.02144949645918115</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1058,7 +1058,7 @@
         <v>24.886296603431646</v>
       </c>
       <c r="H8" s="0">
-        <v>17.560142406627179</v>
+        <v>24.886296603431646</v>
       </c>
       <c r="I8" s="0">
         <v>-8.4055178970657511</v>
@@ -1067,7 +1067,7 @@
         <v>-8.4055178970657511</v>
       </c>
       <c r="K8" s="0">
-        <v>-6.0885923685488503</v>
+        <v>-8.4055178970657511</v>
       </c>
       <c r="L8" s="0">
         <v>1.8316019878865235</v>
@@ -1076,7 +1076,7 @@
         <v>1.8316019878865235</v>
       </c>
       <c r="N8" s="0">
-        <v>1.8012791521412292</v>
+        <v>1.8316019878865235</v>
       </c>
       <c r="O8" s="0">
         <v>1</v>
@@ -1103,7 +1103,7 @@
         <v>0</v>
       </c>
       <c r="W8" s="0">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="X8" s="0">
         <v>100</v>
@@ -1115,10 +1115,10 @@
         <v>100</v>
       </c>
       <c r="AA8" s="0">
-        <v>77.817460317460345</v>
+        <v>100</v>
       </c>
       <c r="AB8" s="0">
-        <v>6.0999999999999988</v>
+        <v>0</v>
       </c>
       <c r="AC8" s="0">
         <v>0</v>
@@ -1127,7 +1127,7 @@
         <v>0</v>
       </c>
       <c r="AE8" s="0">
-        <v>-7.3261541968044686</v>
+        <v>0</v>
       </c>
       <c r="AF8" s="0">
         <v>0</v>
@@ -1136,7 +1136,7 @@
         <v>0</v>
       </c>
       <c r="AH8" s="0">
-        <v>2.3169255285168999</v>
+        <v>0</v>
       </c>
       <c r="AI8" s="0">
         <v>0</v>
@@ -1145,7 +1145,7 @@
         <v>0</v>
       </c>
       <c r="AK8" s="0">
-        <v>-0.030322835745294263</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1171,7 +1171,7 @@
         <v>16.702577170503385</v>
       </c>
       <c r="H9" s="0">
-        <v>8.4690283957127086</v>
+        <v>15.34030138288931</v>
       </c>
       <c r="I9" s="0">
         <v>-18.755277437767138</v>
@@ -1180,7 +1180,7 @@
         <v>-18.755277437767138</v>
       </c>
       <c r="K9" s="0">
-        <v>-14.200548002191216</v>
+        <v>-19.801000033164318</v>
       </c>
       <c r="L9" s="0">
         <v>0.89546472171375724</v>
@@ -1189,7 +1189,7 @@
         <v>0.89546472171375724</v>
       </c>
       <c r="N9" s="0">
-        <v>0.68956474035617243</v>
+        <v>0.84827711766152403</v>
       </c>
       <c r="O9" s="0">
         <v>1</v>
@@ -1216,7 +1216,7 @@
         <v>0</v>
       </c>
       <c r="W9" s="0">
-        <v>41</v>
+        <v>6</v>
       </c>
       <c r="X9" s="0">
         <v>100</v>
@@ -1228,10 +1228,10 @@
         <v>100</v>
       </c>
       <c r="AA9" s="0">
-        <v>77.30000000000004</v>
+        <v>99</v>
       </c>
       <c r="AB9" s="0">
-        <v>7.5999999999999988</v>
+        <v>2</v>
       </c>
       <c r="AC9" s="0">
         <v>0</v>
@@ -1240,7 +1240,7 @@
         <v>0</v>
       </c>
       <c r="AE9" s="0">
-        <v>-8.2335487747906768</v>
+        <v>-1.3622757876140756</v>
       </c>
       <c r="AF9" s="0">
         <v>0</v>
@@ -1249,7 +1249,7 @@
         <v>0</v>
       </c>
       <c r="AH9" s="0">
-        <v>4.554729435575922</v>
+        <v>-1.0457225953971805</v>
       </c>
       <c r="AI9" s="0">
         <v>0</v>
@@ -1258,7 +1258,7 @@
         <v>0</v>
       </c>
       <c r="AK9" s="0">
-        <v>-0.2058999813575848</v>
+        <v>-0.047187604052233212</v>
       </c>
     </row>
     <row r="10">
@@ -1284,7 +1284,7 @@
         <v>10.932367433130064</v>
       </c>
       <c r="H10" s="0">
-        <v>8.8050500761055019</v>
+        <v>10.932367433130064</v>
       </c>
       <c r="I10" s="0">
         <v>-9.1331291607355318</v>
@@ -1293,7 +1293,7 @@
         <v>-9.1331291607355318</v>
       </c>
       <c r="K10" s="0">
-        <v>-7.4670309512922639</v>
+        <v>-9.1331291607355318</v>
       </c>
       <c r="L10" s="0">
         <v>1.968059254099956</v>
@@ -1302,7 +1302,7 @@
         <v>1.968059254099956</v>
       </c>
       <c r="N10" s="0">
-        <v>2.0960494697801262</v>
+        <v>1.968059254099956</v>
       </c>
       <c r="O10" s="0">
         <v>1</v>
@@ -1329,7 +1329,7 @@
         <v>0</v>
       </c>
       <c r="W10" s="0">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="X10" s="0">
         <v>100</v>
@@ -1341,10 +1341,10 @@
         <v>100</v>
       </c>
       <c r="AA10" s="0">
-        <v>77.79411764705884</v>
+        <v>100</v>
       </c>
       <c r="AB10" s="0">
-        <v>2.2999999999999998</v>
+        <v>0</v>
       </c>
       <c r="AC10" s="0">
         <v>0</v>
@@ -1353,7 +1353,7 @@
         <v>0</v>
       </c>
       <c r="AE10" s="0">
-        <v>-2.1273173570245607</v>
+        <v>0</v>
       </c>
       <c r="AF10" s="0">
         <v>0</v>
@@ -1362,7 +1362,7 @@
         <v>0</v>
       </c>
       <c r="AH10" s="0">
-        <v>1.6660982094432675</v>
+        <v>0</v>
       </c>
       <c r="AI10" s="0">
         <v>0</v>
@@ -1371,7 +1371,7 @@
         <v>0</v>
       </c>
       <c r="AK10" s="0">
-        <v>0.12799021568017022</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/results/walkforward/walk_forward_SPY.xlsx
+++ b/results/walkforward/walk_forward_SPY.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="330" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="514" uniqueCount="48">
   <si>
     <t>Ticker</t>
   </si>
@@ -377,10 +377,10 @@
         <v>-4.5690856356264682</v>
       </c>
       <c r="G2" s="0">
-        <v>-5.3677709816334573</v>
+        <v>-4.5690856356264682</v>
       </c>
       <c r="H2" s="0">
-        <v>-8.8923616416908597</v>
+        <v>-8.0023602085733891</v>
       </c>
       <c r="I2" s="0">
         <v>-19.351436257194486</v>
@@ -389,16 +389,16 @@
         <v>-19.351436257194486</v>
       </c>
       <c r="K2" s="0">
-        <v>-18.463481532639747</v>
+        <v>-19.3721467406769</v>
       </c>
       <c r="L2" s="0">
         <v>-0.19029490039202343</v>
       </c>
       <c r="M2" s="0">
-        <v>-0.24047415976865014</v>
+        <v>-0.19029490039202343</v>
       </c>
       <c r="N2" s="0">
-        <v>-0.50205518718021203</v>
+        <v>-0.42222161957838694</v>
       </c>
       <c r="O2" s="0">
         <v>1</v>
@@ -413,43 +413,43 @@
         <v>0</v>
       </c>
       <c r="S2" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T2" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U2" s="0">
         <v>0</v>
       </c>
       <c r="V2" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W2" s="0">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="X2" s="0">
         <v>100</v>
       </c>
       <c r="Y2" s="0">
-        <v>98.804780876494021</v>
+        <v>100</v>
       </c>
       <c r="Z2" s="0">
-        <v>98.804780876494021</v>
+        <v>100</v>
       </c>
       <c r="AA2" s="0">
-        <v>97.111553784860561</v>
+        <v>98.406374501992033</v>
       </c>
       <c r="AB2" s="0">
-        <v>3.5</v>
+        <v>1.5</v>
       </c>
       <c r="AC2" s="0">
         <v>0</v>
       </c>
       <c r="AD2" s="0">
-        <v>-0.79868534600698871</v>
+        <v>0</v>
       </c>
       <c r="AE2" s="0">
-        <v>-4.3232760060643916</v>
+        <v>-3.4332745729469205</v>
       </c>
       <c r="AF2" s="0">
         <v>0</v>
@@ -458,16 +458,16 @@
         <v>0</v>
       </c>
       <c r="AH2" s="0">
-        <v>0.88795472455474034</v>
+        <v>-0.020710483482411224</v>
       </c>
       <c r="AI2" s="0">
         <v>0</v>
       </c>
       <c r="AJ2" s="0">
-        <v>-0.050179259376626706</v>
+        <v>0</v>
       </c>
       <c r="AK2" s="0">
-        <v>-0.31176028678818857</v>
+        <v>-0.23192671918636351</v>
       </c>
     </row>
     <row r="3">
@@ -490,10 +490,10 @@
         <v>31.221575745812657</v>
       </c>
       <c r="G3" s="0">
-        <v>27.598956642708174</v>
+        <v>31.221575745812657</v>
       </c>
       <c r="H3" s="0">
-        <v>27.598956642708174</v>
+        <v>31.089532766683693</v>
       </c>
       <c r="I3" s="0">
         <v>-6.6194338784514422</v>
@@ -502,25 +502,25 @@
         <v>-6.6194338784514422</v>
       </c>
       <c r="K3" s="0">
-        <v>-6.6194338784514422</v>
+        <v>-6.6194338784514306</v>
       </c>
       <c r="L3" s="0">
         <v>2.235235634639432</v>
       </c>
       <c r="M3" s="0">
-        <v>2.1299387976520467</v>
+        <v>2.235235634639432</v>
       </c>
       <c r="N3" s="0">
-        <v>2.1299387976520467</v>
+        <v>2.2270993973017106</v>
       </c>
       <c r="O3" s="0">
         <v>1</v>
       </c>
       <c r="P3" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q3" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R3" s="0">
         <v>0</v>
@@ -535,34 +535,34 @@
         <v>0</v>
       </c>
       <c r="V3" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W3" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X3" s="0">
         <v>100</v>
       </c>
       <c r="Y3" s="0">
-        <v>98.412698412698404</v>
+        <v>100</v>
       </c>
       <c r="Z3" s="0">
-        <v>98.412698412698404</v>
+        <v>100</v>
       </c>
       <c r="AA3" s="0">
-        <v>98.412698412698404</v>
+        <v>100</v>
       </c>
       <c r="AB3" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC3" s="0">
         <v>0</v>
       </c>
       <c r="AD3" s="0">
-        <v>-3.6226191031044852</v>
+        <v>0</v>
       </c>
       <c r="AE3" s="0">
-        <v>-3.6226191031044852</v>
+        <v>-0.13204297912896568</v>
       </c>
       <c r="AF3" s="0">
         <v>0</v>
@@ -571,16 +571,16 @@
         <v>0</v>
       </c>
       <c r="AH3" s="0">
-        <v>0</v>
+        <v>1.1102230246251565e-14</v>
       </c>
       <c r="AI3" s="0">
         <v>0</v>
       </c>
       <c r="AJ3" s="0">
-        <v>-0.10529683698738523</v>
+        <v>0</v>
       </c>
       <c r="AK3" s="0">
-        <v>-0.10529683698738523</v>
+        <v>-0.008136237337721397</v>
       </c>
     </row>
     <row r="4">
@@ -603,28 +603,28 @@
         <v>18.335809706936089</v>
       </c>
       <c r="G4" s="0">
-        <v>44.259680131501035</v>
+        <v>38.682879360126222</v>
       </c>
       <c r="H4" s="0">
-        <v>41.868006425993244</v>
+        <v>41.858408421578574</v>
       </c>
       <c r="I4" s="0">
         <v>-33.715385820778579</v>
       </c>
       <c r="J4" s="0">
+        <v>-13.518961923504635</v>
+      </c>
+      <c r="K4" s="0">
         <v>-12.430243974198675</v>
-      </c>
-      <c r="K4" s="0">
-        <v>-12.452228914892061</v>
       </c>
       <c r="L4" s="0">
         <v>0.67018718454210757</v>
       </c>
       <c r="M4" s="0">
-        <v>1.7876808309470249</v>
+        <v>1.60947251735417</v>
       </c>
       <c r="N4" s="0">
-        <v>1.7730547926263396</v>
+        <v>1.7512634821607103</v>
       </c>
       <c r="O4" s="0">
         <v>1</v>
@@ -651,7 +651,7 @@
         <v>2</v>
       </c>
       <c r="W4" s="0">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="X4" s="0">
         <v>100</v>
@@ -663,37 +663,37 @@
         <v>92.490118577075094</v>
       </c>
       <c r="AA4" s="0">
-        <v>91.699604743083</v>
+        <v>91.897233201581031</v>
       </c>
       <c r="AB4" s="0">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="AC4" s="0">
         <v>0</v>
       </c>
       <c r="AD4" s="0">
-        <v>25.923870424564942</v>
+        <v>20.347069653190132</v>
       </c>
       <c r="AE4" s="0">
-        <v>23.532196719057154</v>
+        <v>23.522598714642484</v>
       </c>
       <c r="AF4" s="0">
         <v>0</v>
       </c>
       <c r="AG4" s="0">
+        <v>20.196423897273942</v>
+      </c>
+      <c r="AH4" s="0">
         <v>21.285141846579904</v>
       </c>
-      <c r="AH4" s="0">
-        <v>21.263156905886515</v>
-      </c>
       <c r="AI4" s="0">
         <v>0</v>
       </c>
       <c r="AJ4" s="0">
-        <v>1.1174936464049172</v>
+        <v>0.93928533281206239</v>
       </c>
       <c r="AK4" s="0">
-        <v>1.1028676080842321</v>
+        <v>1.0810762976186026</v>
       </c>
     </row>
     <row r="5">
@@ -829,97 +829,97 @@
         <v>-18.172028536815223</v>
       </c>
       <c r="G6" s="0">
-        <v>-15.637795904287955</v>
+        <v>-18.172028536815223</v>
       </c>
       <c r="H6" s="0">
-        <v>-17.834736263905871</v>
+        <v>-24.139391857752056</v>
       </c>
       <c r="I6" s="0">
         <v>-24.495450885579995</v>
       </c>
       <c r="J6" s="0">
-        <v>-24.07360476659418</v>
+        <v>-24.495450885579995</v>
       </c>
       <c r="K6" s="0">
-        <v>-24.894281809042052</v>
+        <v>-30.001674110873722</v>
       </c>
       <c r="L6" s="0">
         <v>-0.70940817269533907</v>
       </c>
       <c r="M6" s="0">
-        <v>-0.68843779145003703</v>
+        <v>-0.70940817269533907</v>
       </c>
       <c r="N6" s="0">
-        <v>-0.8262770064734658</v>
+        <v>-1.0657518350180681</v>
       </c>
       <c r="O6" s="0">
         <v>1</v>
       </c>
       <c r="P6" s="0">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q6" s="0">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R6" s="0">
         <v>0</v>
       </c>
       <c r="S6" s="0">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T6" s="0">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U6" s="0">
         <v>0</v>
       </c>
       <c r="V6" s="0">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W6" s="0">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="X6" s="0">
         <v>100</v>
       </c>
       <c r="Y6" s="0">
-        <v>82.470119521912352</v>
+        <v>100</v>
       </c>
       <c r="Z6" s="0">
-        <v>82.470119521912352</v>
+        <v>100</v>
       </c>
       <c r="AA6" s="0">
-        <v>80.478087649402383</v>
+        <v>96.613545816733065</v>
       </c>
       <c r="AB6" s="0">
-        <v>6.5</v>
+        <v>3.5</v>
       </c>
       <c r="AC6" s="0">
         <v>0</v>
       </c>
       <c r="AD6" s="0">
-        <v>2.5342326325272668</v>
+        <v>0</v>
       </c>
       <c r="AE6" s="0">
-        <v>0.33729227290935082</v>
+        <v>-5.967363320936836</v>
       </c>
       <c r="AF6" s="0">
         <v>0</v>
       </c>
       <c r="AG6" s="0">
-        <v>0.42184611898581359</v>
+        <v>0</v>
       </c>
       <c r="AH6" s="0">
-        <v>-0.39883092346205684</v>
+        <v>-5.5062232252937271</v>
       </c>
       <c r="AI6" s="0">
         <v>0</v>
       </c>
       <c r="AJ6" s="0">
-        <v>0.020970381245302039</v>
+        <v>0</v>
       </c>
       <c r="AK6" s="0">
-        <v>-0.11686883377812674</v>
+        <v>-0.35634366232272907</v>
       </c>
     </row>
     <row r="7">
@@ -1171,7 +1171,7 @@
         <v>16.702577170503385</v>
       </c>
       <c r="H9" s="0">
-        <v>15.34030138288931</v>
+        <v>17.774873089791178</v>
       </c>
       <c r="I9" s="0">
         <v>-18.755277437767138</v>
@@ -1180,7 +1180,7 @@
         <v>-18.755277437767138</v>
       </c>
       <c r="K9" s="0">
-        <v>-19.801000033164318</v>
+        <v>-19.14146047812514</v>
       </c>
       <c r="L9" s="0">
         <v>0.89546472171375724</v>
@@ -1189,7 +1189,7 @@
         <v>0.89546472171375724</v>
       </c>
       <c r="N9" s="0">
-        <v>0.84827711766152403</v>
+        <v>0.96079510518661948</v>
       </c>
       <c r="O9" s="0">
         <v>1</v>
@@ -1216,7 +1216,7 @@
         <v>0</v>
       </c>
       <c r="W9" s="0">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X9" s="0">
         <v>100</v>
@@ -1228,10 +1228,10 @@
         <v>100</v>
       </c>
       <c r="AA9" s="0">
-        <v>99</v>
+        <v>98.900000000000006</v>
       </c>
       <c r="AB9" s="0">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AC9" s="0">
         <v>0</v>
@@ -1240,7 +1240,7 @@
         <v>0</v>
       </c>
       <c r="AE9" s="0">
-        <v>-1.3622757876140756</v>
+        <v>1.0722959192877912</v>
       </c>
       <c r="AF9" s="0">
         <v>0</v>
@@ -1249,7 +1249,7 @@
         <v>0</v>
       </c>
       <c r="AH9" s="0">
-        <v>-1.0457225953971805</v>
+        <v>-0.38618304035800133</v>
       </c>
       <c r="AI9" s="0">
         <v>0</v>
@@ -1258,7 +1258,7 @@
         <v>0</v>
       </c>
       <c r="AK9" s="0">
-        <v>-0.047187604052233212</v>
+        <v>0.065330383472862241</v>
       </c>
     </row>
     <row r="10">
